--- a/MAJSushiConfig/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-procedure-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-procedure-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>priority</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-procedure-priority-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-procedure-priority-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -546,7 +546,7 @@
     <t>Procedure.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-body-structure-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-body-structure-document|0.1.0)
 </t>
   </si>
   <si>
@@ -565,7 +565,7 @@
     <t>participant</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -620,7 +620,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
   </si>
   <si>
     <t>Procedure.extension:participant.extension:typeCode</t>
@@ -666,14 +666,14 @@
     <t>Procedure.extension:participant.extension:actor.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
 </t>
   </si>
   <si>
     <t>Procedure.extension:participant.url</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
     <t>Procedure.extension:participant.value[x]</t>
@@ -689,7 +689,7 @@
     <t>difficulte</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-procedure-difficulty-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-procedure-difficulty-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -817,7 +817,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-administration-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-procedure-document|0.1.0)
+    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-procedure-document|0.1.0)
 </t>
   </si>
   <si>
@@ -938,7 +938,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-procedure-code|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-procedure-code|0.1.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -960,7 +960,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -985,7 +985,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-encounter-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-encounter-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1056,7 +1056,7 @@
     <t>Procedure.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-related-person-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-related-person-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1150,7 +1150,7 @@
     <t>Procedure.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|Device|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1246,7 +1246,7 @@
     <t>Procedure.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-diagnostic-report-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-diagnostic-report-imaging-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-diagnostic-report-bio-chapter-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-imaging-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-bio-chapter-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1838,7 +1838,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.6328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
